--- a/For Drug Challenge/Simulation_Results_Log.xlsx
+++ b/For Drug Challenge/Simulation_Results_Log.xlsx
@@ -457,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.21875" customWidth="true"/>
@@ -1198,6 +1198,136 @@
         <v>2767.5256230875475</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>4</v>
+      </c>
+      <c r="B12" s="0">
+        <v>1</v>
+      </c>
+      <c r="C12" s="0">
+        <v>10</v>
+      </c>
+      <c r="D12" s="0">
+        <v>52.813785983823543</v>
+      </c>
+      <c r="E12" s="0">
+        <v>569.71450534793803</v>
+      </c>
+      <c r="F12" s="0">
+        <v>226.70093110920425</v>
+      </c>
+      <c r="G12" s="0">
+        <v>66.0259501317569</v>
+      </c>
+      <c r="H12" s="0">
+        <v>26.380314939850237</v>
+      </c>
+      <c r="I12" s="0">
+        <v>7.5937349283928661</v>
+      </c>
+      <c r="J12" s="0">
+        <v>540.35338323200961</v>
+      </c>
+      <c r="K12" s="0">
+        <v>540.36980386814605</v>
+      </c>
+      <c r="L12" s="0">
+        <v>0.83294297381631766</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0.16705702618368234</v>
+      </c>
+      <c r="N12" s="0">
+        <v>0.89005610660786549</v>
+      </c>
+      <c r="O12" s="0">
+        <v>-75.726647237186711</v>
+      </c>
+      <c r="P12" s="0">
+        <v>114.68444047216002</v>
+      </c>
+      <c r="Q12" s="0">
+        <v>38.957793234973302</v>
+      </c>
+      <c r="R12" s="0">
+        <v>127.93451211941007</v>
+      </c>
+      <c r="S12" s="0">
+        <v>2467.993240405478</v>
+      </c>
+      <c r="T12" s="0">
+        <v>2657.6439481351917</v>
+      </c>
+      <c r="U12" s="0">
+        <v>2767.5256230875475</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>4</v>
+      </c>
+      <c r="B13" s="0">
+        <v>1</v>
+      </c>
+      <c r="C13" s="0">
+        <v>10</v>
+      </c>
+      <c r="D13" s="0">
+        <v>52.792401451961538</v>
+      </c>
+      <c r="E13" s="0">
+        <v>569.26304975057553</v>
+      </c>
+      <c r="F13" s="0">
+        <v>227.06954161488375</v>
+      </c>
+      <c r="G13" s="0">
+        <v>62.797752439863572</v>
+      </c>
+      <c r="H13" s="0">
+        <v>29.531744147006233</v>
+      </c>
+      <c r="I13" s="0">
+        <v>7.6705034131301826</v>
+      </c>
+      <c r="J13" s="0">
+        <v>434.95634414083776</v>
+      </c>
+      <c r="K13" s="0">
+        <v>434.96314968078821</v>
+      </c>
+      <c r="L13" s="0">
+        <v>0.57331737923927473</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0.42668262076072527</v>
+      </c>
+      <c r="N13" s="0">
+        <v>0.90655680566951558</v>
+      </c>
+      <c r="O13" s="0">
+        <v>-75.726647237186711</v>
+      </c>
+      <c r="P13" s="0">
+        <v>114.68444047216002</v>
+      </c>
+      <c r="Q13" s="0">
+        <v>38.957793234973302</v>
+      </c>
+      <c r="R13" s="0">
+        <v>127.93451211941007</v>
+      </c>
+      <c r="S13" s="0">
+        <v>2467.993240405478</v>
+      </c>
+      <c r="T13" s="0">
+        <v>2657.6439481351917</v>
+      </c>
+      <c r="U13" s="0">
+        <v>2767.5256230875475</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/For Drug Challenge/Simulation_Results_Log.xlsx
+++ b/For Drug Challenge/Simulation_Results_Log.xlsx
@@ -457,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.21875" customWidth="true"/>
@@ -466,8 +466,8 @@
     <col min="4" max="4" width="14.33203125" customWidth="true"/>
     <col min="5" max="5" width="11.5546875" customWidth="true"/>
     <col min="11" max="11" width="11.77734375" customWidth="true"/>
-    <col min="12" max="12" width="13.5546875" customWidth="true"/>
-    <col min="13" max="13" width="12.5546875" customWidth="true"/>
+    <col min="12" max="12" width="15.5546875" customWidth="true"/>
+    <col min="13" max="13" width="15.5546875" customWidth="true"/>
     <col min="14" max="14" width="18.5546875" customWidth="true"/>
     <col min="15" max="15" width="12.21875" customWidth="true"/>
     <col min="16" max="16" width="11.5546875" customWidth="true"/>
@@ -1328,6 +1328,396 @@
         <v>2767.5256230875475</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>4</v>
+      </c>
+      <c r="B14" s="0">
+        <v>1</v>
+      </c>
+      <c r="C14" s="0">
+        <v>10</v>
+      </c>
+      <c r="D14" s="0">
+        <v>52.7957054202259</v>
+      </c>
+      <c r="E14" s="0">
+        <v>569.71450534793803</v>
+      </c>
+      <c r="F14" s="0">
+        <v>226.70093110920425</v>
+      </c>
+      <c r="G14" s="0">
+        <v>62.759924633748618</v>
+      </c>
+      <c r="H14" s="0">
+        <v>29.574704696271819</v>
+      </c>
+      <c r="I14" s="0">
+        <v>7.6653706699795636</v>
+      </c>
+      <c r="J14" s="0">
+        <v>435.04092841277804</v>
+      </c>
+      <c r="K14" s="0">
+        <v>435.19172903845305</v>
+      </c>
+      <c r="L14" s="0">
+        <v>0.56841519913478067</v>
+      </c>
+      <c r="M14" s="0">
+        <v>0.43158480086521933</v>
+      </c>
+      <c r="N14" s="0">
+        <v>0.90696978246767013</v>
+      </c>
+      <c r="O14" s="0">
+        <v>-75.726647237186711</v>
+      </c>
+      <c r="P14" s="0">
+        <v>114.658369300025</v>
+      </c>
+      <c r="Q14" s="0">
+        <v>38.93172206283829</v>
+      </c>
+      <c r="R14" s="0">
+        <v>127.93451211941007</v>
+      </c>
+      <c r="S14" s="0">
+        <v>465.99176041045484</v>
+      </c>
+      <c r="T14" s="0">
+        <v>655.54505633357621</v>
+      </c>
+      <c r="U14" s="0">
+        <v>765.27259589526784</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>4</v>
+      </c>
+      <c r="B15" s="0">
+        <v>1</v>
+      </c>
+      <c r="C15" s="0">
+        <v>10</v>
+      </c>
+      <c r="D15" s="0">
+        <v>52.7957054202259</v>
+      </c>
+      <c r="E15" s="0">
+        <v>569.71450534793803</v>
+      </c>
+      <c r="F15" s="0">
+        <v>226.70093110920425</v>
+      </c>
+      <c r="G15" s="0">
+        <v>62.759924633748618</v>
+      </c>
+      <c r="H15" s="0">
+        <v>29.574704696271819</v>
+      </c>
+      <c r="I15" s="0">
+        <v>7.6653706699795636</v>
+      </c>
+      <c r="J15" s="0">
+        <v>435.04092841277804</v>
+      </c>
+      <c r="K15" s="0">
+        <v>435.19172903845305</v>
+      </c>
+      <c r="L15" s="0">
+        <v>0.56841519913478067</v>
+      </c>
+      <c r="M15" s="0">
+        <v>0.43158480086521933</v>
+      </c>
+      <c r="N15" s="0">
+        <v>0.90696978246767013</v>
+      </c>
+      <c r="O15" s="0">
+        <v>-75.726647237186711</v>
+      </c>
+      <c r="P15" s="0">
+        <v>114.74741048291276</v>
+      </c>
+      <c r="Q15" s="0">
+        <v>39.020763245726037</v>
+      </c>
+      <c r="R15" s="0">
+        <v>127.93451211941007</v>
+      </c>
+      <c r="S15" s="0">
+        <v>4467.6248676215509</v>
+      </c>
+      <c r="T15" s="0">
+        <v>4657.9562975431854</v>
+      </c>
+      <c r="U15" s="0">
+        <v>4768.2166551196733</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>4</v>
+      </c>
+      <c r="B16" s="0">
+        <v>1</v>
+      </c>
+      <c r="C16" s="0">
+        <v>10</v>
+      </c>
+      <c r="D16" s="0">
+        <v>52.7957054202259</v>
+      </c>
+      <c r="E16" s="0">
+        <v>569.71450534793803</v>
+      </c>
+      <c r="F16" s="0">
+        <v>226.70093110920425</v>
+      </c>
+      <c r="G16" s="0">
+        <v>62.759924633748618</v>
+      </c>
+      <c r="H16" s="0">
+        <v>29.574704696271819</v>
+      </c>
+      <c r="I16" s="0">
+        <v>7.6653706699795636</v>
+      </c>
+      <c r="J16" s="0">
+        <v>435.04092841277804</v>
+      </c>
+      <c r="K16" s="0">
+        <v>435.19172903845305</v>
+      </c>
+      <c r="L16" s="0">
+        <v>0.56841519913478067</v>
+      </c>
+      <c r="M16" s="0">
+        <v>0.43158480086521933</v>
+      </c>
+      <c r="N16" s="0">
+        <v>0.90696978246767013</v>
+      </c>
+      <c r="O16" s="0">
+        <v>-75.726647237186711</v>
+      </c>
+      <c r="P16" s="0">
+        <v>114.658369300025</v>
+      </c>
+      <c r="Q16" s="0">
+        <v>38.93172206283829</v>
+      </c>
+      <c r="R16" s="0">
+        <v>127.93451211941007</v>
+      </c>
+      <c r="S16" s="0">
+        <v>465.99176041045484</v>
+      </c>
+      <c r="T16" s="0">
+        <v>655.54505633357621</v>
+      </c>
+      <c r="U16" s="0">
+        <v>765.27259589526784</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>4</v>
+      </c>
+      <c r="B17" s="0">
+        <v>1</v>
+      </c>
+      <c r="C17" s="0">
+        <v>10</v>
+      </c>
+      <c r="D17" s="0">
+        <v>52.7957054202259</v>
+      </c>
+      <c r="E17" s="0">
+        <v>569.71450534793803</v>
+      </c>
+      <c r="F17" s="0">
+        <v>226.70093110920425</v>
+      </c>
+      <c r="G17" s="0">
+        <v>62.759924633748618</v>
+      </c>
+      <c r="H17" s="0">
+        <v>29.574704696271819</v>
+      </c>
+      <c r="I17" s="0">
+        <v>7.6653706699795636</v>
+      </c>
+      <c r="J17" s="0">
+        <v>435.04092841277804</v>
+      </c>
+      <c r="K17" s="0">
+        <v>435.19172903845305</v>
+      </c>
+      <c r="L17" s="0">
+        <v>0.56841519913478067</v>
+      </c>
+      <c r="M17" s="0">
+        <v>0.43158480086521933</v>
+      </c>
+      <c r="N17" s="0">
+        <v>0.90696978246767013</v>
+      </c>
+      <c r="O17" s="0">
+        <v>-75.726647237186711</v>
+      </c>
+      <c r="P17" s="0">
+        <v>114.658369300025</v>
+      </c>
+      <c r="Q17" s="0">
+        <v>38.93172206283829</v>
+      </c>
+      <c r="R17" s="0">
+        <v>127.93451211941007</v>
+      </c>
+      <c r="S17" s="0">
+        <v>465.99176041045484</v>
+      </c>
+      <c r="T17" s="0">
+        <v>655.54505633357621</v>
+      </c>
+      <c r="U17" s="0">
+        <v>765.27259589526784</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>0</v>
+      </c>
+      <c r="B18" s="0">
+        <v>1</v>
+      </c>
+      <c r="C18" s="0">
+        <v>10</v>
+      </c>
+      <c r="D18" s="0">
+        <v>52.423897879396485</v>
+      </c>
+      <c r="E18" s="0">
+        <v>558.98163463424089</v>
+      </c>
+      <c r="F18" s="0">
+        <v>207.16911364893531</v>
+      </c>
+      <c r="G18" s="0">
+        <v>58.078230058856541</v>
+      </c>
+      <c r="H18" s="0">
+        <v>34.33191687218833</v>
+      </c>
+      <c r="I18" s="0">
+        <v>7.5898530689551365</v>
+      </c>
+      <c r="J18" s="0">
+        <v>294.0459577270916</v>
+      </c>
+      <c r="K18" s="0">
+        <v>294.04610323059131</v>
+      </c>
+      <c r="L18" s="0">
+        <v>0.00035894509320821832</v>
+      </c>
+      <c r="M18" s="0">
+        <v>0.99964105490679178</v>
+      </c>
+      <c r="N18" s="0">
+        <v>0.89752180991683594</v>
+      </c>
+      <c r="O18" s="0">
+        <v>-75.73917575411194</v>
+      </c>
+      <c r="P18" s="0">
+        <v>113.68590268996741</v>
+      </c>
+      <c r="Q18" s="0">
+        <v>37.946726935855466</v>
+      </c>
+      <c r="R18" s="0">
+        <v>134.69991731651683</v>
+      </c>
+      <c r="S18" s="0">
+        <v>336.37451649255672</v>
+      </c>
+      <c r="T18" s="0">
+        <v>401.33901247254289</v>
+      </c>
+      <c r="U18" s="0">
+        <v>443.10608322380904</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>0</v>
+      </c>
+      <c r="B19" s="0">
+        <v>1</v>
+      </c>
+      <c r="C19" s="0">
+        <v>5</v>
+      </c>
+      <c r="D19" s="0">
+        <v>52.393601198791146</v>
+      </c>
+      <c r="E19" s="0">
+        <v>560.23469367993721</v>
+      </c>
+      <c r="F19" s="0">
+        <v>206.82392782405259</v>
+      </c>
+      <c r="G19" s="0">
+        <v>58.090141682841512</v>
+      </c>
+      <c r="H19" s="0">
+        <v>34.323330318229772</v>
+      </c>
+      <c r="I19" s="0">
+        <v>7.586527998928724</v>
+      </c>
+      <c r="J19" s="0">
+        <v>294.03003381735476</v>
+      </c>
+      <c r="K19" s="0">
+        <v>300.04612901284111</v>
+      </c>
+      <c r="L19" s="0">
+        <v>0.99963856557421904</v>
+      </c>
+      <c r="M19" s="0">
+        <v>0.00036143442578095986</v>
+      </c>
+      <c r="N19" s="0">
+        <v>0.89731328156226975</v>
+      </c>
+      <c r="O19" s="0">
+        <v>-75.739175625440481</v>
+      </c>
+      <c r="P19" s="0">
+        <v>113.57898015447321</v>
+      </c>
+      <c r="Q19" s="0">
+        <v>37.839804529032726</v>
+      </c>
+      <c r="R19" s="0">
+        <v>133.59022835623125</v>
+      </c>
+      <c r="S19" s="0">
+        <v>337.9121898585372</v>
+      </c>
+      <c r="T19" s="0">
+        <v>403.08953885191977</v>
+      </c>
+      <c r="U19" s="0">
+        <v>445.15774089237721</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/For Drug Challenge/Simulation_Results_Log.xlsx
+++ b/For Drug Challenge/Simulation_Results_Log.xlsx
@@ -457,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U46"/>
   <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.21875" customWidth="true"/>
@@ -1718,6 +1718,1761 @@
         <v>445.15774089237721</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>4</v>
+      </c>
+      <c r="B20" s="0">
+        <v>1</v>
+      </c>
+      <c r="C20" s="0">
+        <v>5</v>
+      </c>
+      <c r="D20" s="0">
+        <v>52.826971127989751</v>
+      </c>
+      <c r="E20" s="0">
+        <v>567.30291921216383</v>
+      </c>
+      <c r="F20" s="0">
+        <v>227.60488556792188</v>
+      </c>
+      <c r="G20" s="0">
+        <v>62.848316588018761</v>
+      </c>
+      <c r="H20" s="0">
+        <v>29.487843967249912</v>
+      </c>
+      <c r="I20" s="0">
+        <v>7.6638394447313445</v>
+      </c>
+      <c r="J20" s="0">
+        <v>436.38470631902612</v>
+      </c>
+      <c r="K20" s="0">
+        <v>436.49541545005525</v>
+      </c>
+      <c r="L20" s="0">
+        <v>0.5571380704472958</v>
+      </c>
+      <c r="M20" s="0">
+        <v>0.4428619295527042</v>
+      </c>
+      <c r="N20" s="0">
+        <v>0.90750145601083854</v>
+      </c>
+      <c r="O20" s="0">
+        <v>-75.726646341835632</v>
+      </c>
+      <c r="P20" s="0">
+        <v>114.78573468014113</v>
+      </c>
+      <c r="Q20" s="0">
+        <v>39.059088338305493</v>
+      </c>
+      <c r="R20" s="0">
+        <v>129.90011005746308</v>
+      </c>
+      <c r="S20" s="0">
+        <v>466.78597574472951</v>
+      </c>
+      <c r="T20" s="0">
+        <v>659.21243020389556</v>
+      </c>
+      <c r="U20" s="0">
+        <v>774.87230480672224</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>4</v>
+      </c>
+      <c r="B21" s="0">
+        <v>2</v>
+      </c>
+      <c r="C21" s="0">
+        <v>100</v>
+      </c>
+      <c r="D21" s="0">
+        <v>41.40365262048288</v>
+      </c>
+      <c r="E21" s="0">
+        <v>238.16853255191845</v>
+      </c>
+      <c r="F21" s="0">
+        <v>150.34456704207514</v>
+      </c>
+      <c r="G21" s="0">
+        <v>51.371923422282229</v>
+      </c>
+      <c r="H21" s="0">
+        <v>39.674692829065847</v>
+      </c>
+      <c r="I21" s="0">
+        <v>8.9533837486519339</v>
+      </c>
+      <c r="J21" s="0">
+        <v>335.61384261778937</v>
+      </c>
+      <c r="K21" s="0">
+        <v>336.27102037069312</v>
+      </c>
+      <c r="L21" s="0">
+        <v>0.99338070630722219</v>
+      </c>
+      <c r="M21" s="0">
+        <v>0.0066192936927778057</v>
+      </c>
+      <c r="N21" s="0">
+        <v>0.94731686240088075</v>
+      </c>
+      <c r="O21" s="0">
+        <v>-75.728306505934214</v>
+      </c>
+      <c r="P21" s="0">
+        <v>101.72347712706893</v>
+      </c>
+      <c r="Q21" s="0">
+        <v>25.995170621134719</v>
+      </c>
+      <c r="R21" s="0">
+        <v>120.83664074157809</v>
+      </c>
+      <c r="S21" s="0">
+        <v>315.68618693150256</v>
+      </c>
+      <c r="T21" s="0">
+        <v>382.06180417068572</v>
+      </c>
+      <c r="U21" s="0">
+        <v>446.64819730462841</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>3</v>
+      </c>
+      <c r="B22" s="0">
+        <v>2</v>
+      </c>
+      <c r="C22" s="0">
+        <v>100</v>
+      </c>
+      <c r="D22" s="0">
+        <v>42.410046296115631</v>
+      </c>
+      <c r="E22" s="0">
+        <v>244.58821265232004</v>
+      </c>
+      <c r="F22" s="0">
+        <v>145.74915264056472</v>
+      </c>
+      <c r="G22" s="0">
+        <v>54.246580743629423</v>
+      </c>
+      <c r="H22" s="0">
+        <v>37.085881241176516</v>
+      </c>
+      <c r="I22" s="0">
+        <v>8.667538015194058</v>
+      </c>
+      <c r="J22" s="0">
+        <v>330.79940268905381</v>
+      </c>
+      <c r="K22" s="0">
+        <v>331.16447081000081</v>
+      </c>
+      <c r="L22" s="0">
+        <v>0.97366646906508281</v>
+      </c>
+      <c r="M22" s="0">
+        <v>0.026333530934917193</v>
+      </c>
+      <c r="N22" s="0">
+        <v>0.94377264185548482</v>
+      </c>
+      <c r="O22" s="0">
+        <v>-75.728311126887689</v>
+      </c>
+      <c r="P22" s="0">
+        <v>101.53818620705896</v>
+      </c>
+      <c r="Q22" s="0">
+        <v>25.80987508017127</v>
+      </c>
+      <c r="R22" s="0">
+        <v>106.33793131906278</v>
+      </c>
+      <c r="S22" s="0">
+        <v>316.25262781878337</v>
+      </c>
+      <c r="T22" s="0">
+        <v>379.81453466709536</v>
+      </c>
+      <c r="U22" s="0">
+        <v>435.97307870900113</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>3</v>
+      </c>
+      <c r="B23" s="0">
+        <v>2</v>
+      </c>
+      <c r="C23" s="0">
+        <v>30</v>
+      </c>
+      <c r="D23" s="0">
+        <v>45.950817804433449</v>
+      </c>
+      <c r="E23" s="0">
+        <v>338.13394673697707</v>
+      </c>
+      <c r="F23" s="0">
+        <v>138.73021816510573</v>
+      </c>
+      <c r="G23" s="0">
+        <v>56.65816337758158</v>
+      </c>
+      <c r="H23" s="0">
+        <v>35.035952550074079</v>
+      </c>
+      <c r="I23" s="0">
+        <v>8.3058840723443357</v>
+      </c>
+      <c r="J23" s="0">
+        <v>347.02530327693108</v>
+      </c>
+      <c r="K23" s="0">
+        <v>347.06630606214799</v>
+      </c>
+      <c r="L23" s="0">
+        <v>0.90310601534447499</v>
+      </c>
+      <c r="M23" s="0">
+        <v>0.096893984655525012</v>
+      </c>
+      <c r="N23" s="0">
+        <v>0.93644009883946766</v>
+      </c>
+      <c r="O23" s="0">
+        <v>-75.72792182190139</v>
+      </c>
+      <c r="P23" s="0">
+        <v>108.9450114495869</v>
+      </c>
+      <c r="Q23" s="0">
+        <v>33.217089627685503</v>
+      </c>
+      <c r="R23" s="0">
+        <v>114.84733690896951</v>
+      </c>
+      <c r="S23" s="0">
+        <v>333.60585081258068</v>
+      </c>
+      <c r="T23" s="0">
+        <v>416.53028489894496</v>
+      </c>
+      <c r="U23" s="0">
+        <v>483.46235215608613</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0">
+        <v>3</v>
+      </c>
+      <c r="B24" s="0">
+        <v>2</v>
+      </c>
+      <c r="C24" s="0">
+        <v>30</v>
+      </c>
+      <c r="D24" s="0">
+        <v>46.048839843642412</v>
+      </c>
+      <c r="E24" s="0">
+        <v>339.86264698740229</v>
+      </c>
+      <c r="F24" s="0">
+        <v>139.75126158781859</v>
+      </c>
+      <c r="G24" s="0">
+        <v>56.693788574286607</v>
+      </c>
+      <c r="H24" s="0">
+        <v>35.001552054219147</v>
+      </c>
+      <c r="I24" s="0">
+        <v>8.3046593714942407</v>
+      </c>
+      <c r="J24" s="0">
+        <v>346.29248626295379</v>
+      </c>
+      <c r="K24" s="0">
+        <v>346.2925209071729</v>
+      </c>
+      <c r="L24" s="0">
+        <v>0.9045479728212259</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.095452027178774101</v>
+      </c>
+      <c r="N24" s="0">
+        <v>0.93577151029595207</v>
+      </c>
+      <c r="O24" s="0">
+        <v>-75.72792182190139</v>
+      </c>
+      <c r="P24" s="0">
+        <v>108.64690889767965</v>
+      </c>
+      <c r="Q24" s="0">
+        <v>32.918987075778254</v>
+      </c>
+      <c r="R24" s="0">
+        <v>113.65532839997019</v>
+      </c>
+      <c r="S24" s="0">
+        <v>330.53486203205739</v>
+      </c>
+      <c r="T24" s="0">
+        <v>412.9437377691138</v>
+      </c>
+      <c r="U24" s="0">
+        <v>479.50593878856307</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0">
+        <v>3</v>
+      </c>
+      <c r="B25" s="0">
+        <v>0</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0</v>
+      </c>
+      <c r="D25" s="0">
+        <v>52.683310104961578</v>
+      </c>
+      <c r="E25" s="0">
+        <v>575.35843742030045</v>
+      </c>
+      <c r="F25" s="0">
+        <v>225.92154739570378</v>
+      </c>
+      <c r="G25" s="0">
+        <v>62.613433661686912</v>
+      </c>
+      <c r="H25" s="0">
+        <v>29.712586736306573</v>
+      </c>
+      <c r="I25" s="0">
+        <v>7.6739796020065212</v>
+      </c>
+      <c r="J25" s="0">
+        <v>428.63703442441761</v>
+      </c>
+      <c r="K25" s="0">
+        <v>428.63711291615232</v>
+      </c>
+      <c r="L25" s="0">
+        <v>0.89157714224095397</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.10842285775904599</v>
+      </c>
+      <c r="N25" s="0">
+        <v>0.9058454815455631</v>
+      </c>
+      <c r="O25" s="0">
+        <v>-75.726649148047002</v>
+      </c>
+      <c r="P25" s="0">
+        <v>114.54543085703676</v>
+      </c>
+      <c r="Q25" s="0">
+        <v>38.818781708989754</v>
+      </c>
+      <c r="R25" s="0">
+        <v>124.02373160129694</v>
+      </c>
+      <c r="S25" s="0">
+        <v>465.89361107600052</v>
+      </c>
+      <c r="T25" s="0">
+        <v>651.10009596545024</v>
+      </c>
+      <c r="U25" s="0">
+        <v>751.62700391448379</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0">
+        <v>0</v>
+      </c>
+      <c r="B26" s="0">
+        <v>0</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0</v>
+      </c>
+      <c r="D26" s="0">
+        <v>52.465157044419207</v>
+      </c>
+      <c r="E26" s="0">
+        <v>560.10479306270395</v>
+      </c>
+      <c r="F26" s="0">
+        <v>207.79114482247587</v>
+      </c>
+      <c r="G26" s="0">
+        <v>58.079365683489591</v>
+      </c>
+      <c r="H26" s="0">
+        <v>34.333804452905909</v>
+      </c>
+      <c r="I26" s="0">
+        <v>7.586829863604498</v>
+      </c>
+      <c r="J26" s="0">
+        <v>293.8084808309128</v>
+      </c>
+      <c r="K26" s="0">
+        <v>293.8097075849314</v>
+      </c>
+      <c r="L26" s="0">
+        <v>0.99965079641601262</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.00034920358398737861</v>
+      </c>
+      <c r="N26" s="0">
+        <v>0.89743925887352527</v>
+      </c>
+      <c r="O26" s="0">
+        <v>-75.739175368098273</v>
+      </c>
+      <c r="P26" s="0">
+        <v>113.66644158248604</v>
+      </c>
+      <c r="Q26" s="0">
+        <v>37.927266214387778</v>
+      </c>
+      <c r="R26" s="0">
+        <v>134.44237878512376</v>
+      </c>
+      <c r="S26" s="0">
+        <v>336.31247702544624</v>
+      </c>
+      <c r="T26" s="0">
+        <v>401.38039051250962</v>
+      </c>
+      <c r="U26" s="0">
+        <v>443.32491620492783</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>4</v>
+      </c>
+      <c r="B27" s="0">
+        <v>0</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0</v>
+      </c>
+      <c r="D27" s="0">
+        <v>52.896663960672143</v>
+      </c>
+      <c r="E27" s="0">
+        <v>567.35918931664924</v>
+      </c>
+      <c r="F27" s="0">
+        <v>230.29658185855169</v>
+      </c>
+      <c r="G27" s="0">
+        <v>62.982964710715216</v>
+      </c>
+      <c r="H27" s="0">
+        <v>29.354886726887656</v>
+      </c>
+      <c r="I27" s="0">
+        <v>7.6621485623971211</v>
+      </c>
+      <c r="J27" s="0">
+        <v>439.86576413524534</v>
+      </c>
+      <c r="K27" s="0">
+        <v>439.98390560270315</v>
+      </c>
+      <c r="L27" s="0">
+        <v>0.56635802478735087</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.43364197521264913</v>
+      </c>
+      <c r="N27" s="0">
+        <v>0.90924025746459236</v>
+      </c>
+      <c r="O27" s="0">
+        <v>-75.72664455113474</v>
+      </c>
+      <c r="P27" s="0">
+        <v>114.7700926231777</v>
+      </c>
+      <c r="Q27" s="0">
+        <v>39.043448072042963</v>
+      </c>
+      <c r="R27" s="0">
+        <v>132.66493983060667</v>
+      </c>
+      <c r="S27" s="0">
+        <v>466.37513860366016</v>
+      </c>
+      <c r="T27" s="0">
+        <v>661.96889944872783</v>
+      </c>
+      <c r="U27" s="0">
+        <v>791.29851905423493</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>4</v>
+      </c>
+      <c r="B28" s="0">
+        <v>1</v>
+      </c>
+      <c r="C28" s="0">
+        <v>10</v>
+      </c>
+      <c r="D28" s="0">
+        <v>52.792401451961538</v>
+      </c>
+      <c r="E28" s="0">
+        <v>569.26304975057553</v>
+      </c>
+      <c r="F28" s="0">
+        <v>227.06954161488375</v>
+      </c>
+      <c r="G28" s="0">
+        <v>62.797752439863572</v>
+      </c>
+      <c r="H28" s="0">
+        <v>29.531744147006233</v>
+      </c>
+      <c r="I28" s="0">
+        <v>7.6705034131301826</v>
+      </c>
+      <c r="J28" s="0">
+        <v>434.95634414083776</v>
+      </c>
+      <c r="K28" s="0">
+        <v>434.96314968078821</v>
+      </c>
+      <c r="L28" s="0">
+        <v>0.57331737923927473</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.42668262076072527</v>
+      </c>
+      <c r="N28" s="0">
+        <v>0.90655680566951558</v>
+      </c>
+      <c r="O28" s="0">
+        <v>-75.726647237186711</v>
+      </c>
+      <c r="P28" s="0">
+        <v>114.658369300025</v>
+      </c>
+      <c r="Q28" s="0">
+        <v>38.93172206283829</v>
+      </c>
+      <c r="R28" s="0">
+        <v>127.93451211941007</v>
+      </c>
+      <c r="S28" s="0">
+        <v>465.99176041045484</v>
+      </c>
+      <c r="T28" s="0">
+        <v>655.54505633357621</v>
+      </c>
+      <c r="U28" s="0">
+        <v>765.27259589526784</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>4</v>
+      </c>
+      <c r="B29" s="0">
+        <v>2</v>
+      </c>
+      <c r="C29" s="0">
+        <v>30</v>
+      </c>
+      <c r="D29" s="0">
+        <v>46.459635854523214</v>
+      </c>
+      <c r="E29" s="0">
+        <v>337.48652887460787</v>
+      </c>
+      <c r="F29" s="0">
+        <v>151.66418607009473</v>
+      </c>
+      <c r="G29" s="0">
+        <v>57.873734449510181</v>
+      </c>
+      <c r="H29" s="0">
+        <v>33.889895815590179</v>
+      </c>
+      <c r="I29" s="0">
+        <v>8.2363697348996379</v>
+      </c>
+      <c r="J29" s="0">
+        <v>388.05462701182728</v>
+      </c>
+      <c r="K29" s="0">
+        <v>388.0839445624523</v>
+      </c>
+      <c r="L29" s="0">
+        <v>0.6824540886667555</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0.3175459113332445</v>
+      </c>
+      <c r="N29" s="0">
+        <v>0.9299815999395703</v>
+      </c>
+      <c r="O29" s="0">
+        <v>-75.727917205918246</v>
+      </c>
+      <c r="P29" s="0">
+        <v>109.67082130050375</v>
+      </c>
+      <c r="Q29" s="0">
+        <v>33.942904094585494</v>
+      </c>
+      <c r="R29" s="0">
+        <v>136.21179838861431</v>
+      </c>
+      <c r="S29" s="0">
+        <v>354.37062517424874</v>
+      </c>
+      <c r="T29" s="0">
+        <v>463.398015541934</v>
+      </c>
+      <c r="U29" s="0">
+        <v>548.27540976776436</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>4</v>
+      </c>
+      <c r="B30" s="0">
+        <v>2</v>
+      </c>
+      <c r="C30" s="0">
+        <v>30</v>
+      </c>
+      <c r="D30" s="0">
+        <v>46.678976516520819</v>
+      </c>
+      <c r="E30" s="0">
+        <v>338.93553715880307</v>
+      </c>
+      <c r="F30" s="0">
+        <v>148.14114626752962</v>
+      </c>
+      <c r="G30" s="0">
+        <v>55.607069417618938</v>
+      </c>
+      <c r="H30" s="0">
+        <v>36.05604015318081</v>
+      </c>
+      <c r="I30" s="0">
+        <v>8.3368904292002544</v>
+      </c>
+      <c r="J30" s="0">
+        <v>348.22524907170367</v>
+      </c>
+      <c r="K30" s="0">
+        <v>348.2252657533532</v>
+      </c>
+      <c r="L30" s="0">
+        <v>0.90336825955211819</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.096631740447881809</v>
+      </c>
+      <c r="N30" s="0">
+        <v>0.93588671654457478</v>
+      </c>
+      <c r="O30" s="0">
+        <v>-75.727917205882662</v>
+      </c>
+      <c r="P30" s="0">
+        <v>109.55043488489645</v>
+      </c>
+      <c r="Q30" s="0">
+        <v>33.822517679013792</v>
+      </c>
+      <c r="R30" s="0">
+        <v>134.44300330742001</v>
+      </c>
+      <c r="S30" s="0">
+        <v>330.96540464976897</v>
+      </c>
+      <c r="T30" s="0">
+        <v>417.7807136891488</v>
+      </c>
+      <c r="U30" s="0">
+        <v>496.51275924040874</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>4</v>
+      </c>
+      <c r="B31" s="0">
+        <v>2</v>
+      </c>
+      <c r="C31" s="0">
+        <v>30</v>
+      </c>
+      <c r="D31" s="0">
+        <v>52.621091625646564</v>
+      </c>
+      <c r="E31" s="0">
+        <v>547.82165366939341</v>
+      </c>
+      <c r="F31" s="0">
+        <v>208.34309010939432</v>
+      </c>
+      <c r="G31" s="0">
+        <v>61.569147550195382</v>
+      </c>
+      <c r="H31" s="0">
+        <v>30.65762524009984</v>
+      </c>
+      <c r="I31" s="0">
+        <v>7.7732272097047863</v>
+      </c>
+      <c r="J31" s="0">
+        <v>349.8377875779762</v>
+      </c>
+      <c r="K31" s="0">
+        <v>350.14993036928769</v>
+      </c>
+      <c r="L31" s="0">
+        <v>0.81108598198509507</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0.18891401801490493</v>
+      </c>
+      <c r="N31" s="0">
+        <v>0.91121503158370454</v>
+      </c>
+      <c r="O31" s="0">
+        <v>-75.726644550978051</v>
+      </c>
+      <c r="P31" s="0">
+        <v>114.73037173211557</v>
+      </c>
+      <c r="Q31" s="0">
+        <v>39.003727181137513</v>
+      </c>
+      <c r="R31" s="0">
+        <v>141.52807173724145</v>
+      </c>
+      <c r="S31" s="0">
+        <v>404.38383259317015</v>
+      </c>
+      <c r="T31" s="0">
+        <v>514.65195208940531</v>
+      </c>
+      <c r="U31" s="0">
+        <v>615.45153483349623</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>4</v>
+      </c>
+      <c r="B32" s="0">
+        <v>2</v>
+      </c>
+      <c r="C32" s="0">
+        <v>100</v>
+      </c>
+      <c r="D32" s="0">
+        <v>52.587936164980178</v>
+      </c>
+      <c r="E32" s="0">
+        <v>546.10370796942584</v>
+      </c>
+      <c r="F32" s="0">
+        <v>203.97446886006946</v>
+      </c>
+      <c r="G32" s="0">
+        <v>61.188729956320017</v>
+      </c>
+      <c r="H32" s="0">
+        <v>31.020963084184665</v>
+      </c>
+      <c r="I32" s="0">
+        <v>7.7903069594953074</v>
+      </c>
+      <c r="J32" s="0">
+        <v>332.26799979124871</v>
+      </c>
+      <c r="K32" s="0">
+        <v>332.26803683430927</v>
+      </c>
+      <c r="L32" s="0">
+        <v>0.94461930390781734</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.055380696092182657</v>
+      </c>
+      <c r="N32" s="0">
+        <v>0.91344482961924078</v>
+      </c>
+      <c r="O32" s="0">
+        <v>-75.72664455093097</v>
+      </c>
+      <c r="P32" s="0">
+        <v>114.55455563689266</v>
+      </c>
+      <c r="Q32" s="0">
+        <v>38.827911085961688</v>
+      </c>
+      <c r="R32" s="0">
+        <v>137.96216023837638</v>
+      </c>
+      <c r="S32" s="0">
+        <v>392.01844578350028</v>
+      </c>
+      <c r="T32" s="0">
+        <v>489.60484543930988</v>
+      </c>
+      <c r="U32" s="0">
+        <v>585.76838337551726</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0">
+        <v>4</v>
+      </c>
+      <c r="B33" s="0">
+        <v>2</v>
+      </c>
+      <c r="C33" s="0">
+        <v>100</v>
+      </c>
+      <c r="D33" s="0">
+        <v>43.033981623145117</v>
+      </c>
+      <c r="E33" s="0">
+        <v>245.90464780460007</v>
+      </c>
+      <c r="F33" s="0">
+        <v>158.57099850154918</v>
+      </c>
+      <c r="G33" s="0">
+        <v>55.564862196498567</v>
+      </c>
+      <c r="H33" s="0">
+        <v>35.858247399272905</v>
+      </c>
+      <c r="I33" s="0">
+        <v>8.5768904042285428</v>
+      </c>
+      <c r="J33" s="0">
+        <v>370.53178690548572</v>
+      </c>
+      <c r="K33" s="0">
+        <v>370.53979087118023</v>
+      </c>
+      <c r="L33" s="0">
+        <v>0.99643764783997313</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.0035623521600268715</v>
+      </c>
+      <c r="N33" s="0">
+        <v>0.93310601055802522</v>
+      </c>
+      <c r="O33" s="0">
+        <v>-75.728306505951252</v>
+      </c>
+      <c r="P33" s="0">
+        <v>102.06583718526858</v>
+      </c>
+      <c r="Q33" s="0">
+        <v>26.337530679317329</v>
+      </c>
+      <c r="R33" s="0">
+        <v>120.00139751860456</v>
+      </c>
+      <c r="S33" s="0">
+        <v>341.88178508964302</v>
+      </c>
+      <c r="T33" s="0">
+        <v>423.98296957543243</v>
+      </c>
+      <c r="U33" s="0">
+        <v>493.11108317888102</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0">
+        <v>4</v>
+      </c>
+      <c r="B34" s="0">
+        <v>2</v>
+      </c>
+      <c r="C34" s="0">
+        <v>30</v>
+      </c>
+      <c r="D34" s="0">
+        <v>46.459635854523214</v>
+      </c>
+      <c r="E34" s="0">
+        <v>337.48652887460787</v>
+      </c>
+      <c r="F34" s="0">
+        <v>151.66418607009473</v>
+      </c>
+      <c r="G34" s="0">
+        <v>57.873734449510181</v>
+      </c>
+      <c r="H34" s="0">
+        <v>33.889895815590179</v>
+      </c>
+      <c r="I34" s="0">
+        <v>8.2363697348996379</v>
+      </c>
+      <c r="J34" s="0">
+        <v>388.05462701182728</v>
+      </c>
+      <c r="K34" s="0">
+        <v>388.0839445624523</v>
+      </c>
+      <c r="L34" s="0">
+        <v>0.6824540886667555</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0.3175459113332445</v>
+      </c>
+      <c r="N34" s="0">
+        <v>0.9299815999395703</v>
+      </c>
+      <c r="O34" s="0">
+        <v>-75.727917205918246</v>
+      </c>
+      <c r="P34" s="0">
+        <v>109.67082130050375</v>
+      </c>
+      <c r="Q34" s="0">
+        <v>33.942904094585494</v>
+      </c>
+      <c r="R34" s="0">
+        <v>136.21179838861431</v>
+      </c>
+      <c r="S34" s="0">
+        <v>354.37062517424874</v>
+      </c>
+      <c r="T34" s="0">
+        <v>463.398015541934</v>
+      </c>
+      <c r="U34" s="0">
+        <v>548.27540976776436</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0">
+        <v>4</v>
+      </c>
+      <c r="B35" s="0">
+        <v>0</v>
+      </c>
+      <c r="C35" s="0">
+        <v>0</v>
+      </c>
+      <c r="D35" s="0">
+        <v>52.896663960672143</v>
+      </c>
+      <c r="E35" s="0">
+        <v>567.35918931664924</v>
+      </c>
+      <c r="F35" s="0">
+        <v>230.29658185855169</v>
+      </c>
+      <c r="G35" s="0">
+        <v>62.982964710715216</v>
+      </c>
+      <c r="H35" s="0">
+        <v>29.354886726887656</v>
+      </c>
+      <c r="I35" s="0">
+        <v>7.6621485623971211</v>
+      </c>
+      <c r="J35" s="0">
+        <v>439.86576413524534</v>
+      </c>
+      <c r="K35" s="0">
+        <v>439.98390560270315</v>
+      </c>
+      <c r="L35" s="0">
+        <v>0.56635802478735087</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0.43364197521264913</v>
+      </c>
+      <c r="N35" s="0">
+        <v>0.90924025746459236</v>
+      </c>
+      <c r="O35" s="0">
+        <v>-75.72664455113474</v>
+      </c>
+      <c r="P35" s="0">
+        <v>114.7700926231777</v>
+      </c>
+      <c r="Q35" s="0">
+        <v>39.043448072042963</v>
+      </c>
+      <c r="R35" s="0">
+        <v>132.66493983060667</v>
+      </c>
+      <c r="S35" s="0">
+        <v>466.37513860366016</v>
+      </c>
+      <c r="T35" s="0">
+        <v>661.96889944872783</v>
+      </c>
+      <c r="U35" s="0">
+        <v>791.29851905423493</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0">
+        <v>0</v>
+      </c>
+      <c r="B36" s="0">
+        <v>0</v>
+      </c>
+      <c r="C36" s="0">
+        <v>0</v>
+      </c>
+      <c r="D36" s="0">
+        <v>52.465157044419207</v>
+      </c>
+      <c r="E36" s="0">
+        <v>560.10479306270395</v>
+      </c>
+      <c r="F36" s="0">
+        <v>207.79114482247587</v>
+      </c>
+      <c r="G36" s="0">
+        <v>58.079365683489591</v>
+      </c>
+      <c r="H36" s="0">
+        <v>34.333804452905909</v>
+      </c>
+      <c r="I36" s="0">
+        <v>7.586829863604498</v>
+      </c>
+      <c r="J36" s="0">
+        <v>293.8084808309128</v>
+      </c>
+      <c r="K36" s="0">
+        <v>293.8097075849314</v>
+      </c>
+      <c r="L36" s="0">
+        <v>0.99965079641601262</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0.00034920358398737861</v>
+      </c>
+      <c r="N36" s="0">
+        <v>0.89743925887352527</v>
+      </c>
+      <c r="O36" s="0">
+        <v>-75.739175368098273</v>
+      </c>
+      <c r="P36" s="0">
+        <v>113.66644158248604</v>
+      </c>
+      <c r="Q36" s="0">
+        <v>37.927266214387778</v>
+      </c>
+      <c r="R36" s="0">
+        <v>134.44237878512376</v>
+      </c>
+      <c r="S36" s="0">
+        <v>336.31247702544624</v>
+      </c>
+      <c r="T36" s="0">
+        <v>401.38039051250962</v>
+      </c>
+      <c r="U36" s="0">
+        <v>443.32491620492783</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0">
+        <v>0</v>
+      </c>
+      <c r="B37" s="0">
+        <v>0</v>
+      </c>
+      <c r="C37" s="0">
+        <v>0</v>
+      </c>
+      <c r="D37" s="0">
+        <v>52.647203219321334</v>
+      </c>
+      <c r="E37" s="0">
+        <v>576.77029962658639</v>
+      </c>
+      <c r="F37" s="0">
+        <v>215.0460619192545</v>
+      </c>
+      <c r="G37" s="0">
+        <v>57.852165923522371</v>
+      </c>
+      <c r="H37" s="0">
+        <v>34.59797539205578</v>
+      </c>
+      <c r="I37" s="0">
+        <v>7.5498586844218414</v>
+      </c>
+      <c r="J37" s="0">
+        <v>289.90378277147448</v>
+      </c>
+      <c r="K37" s="0">
+        <v>289.94930407517444</v>
+      </c>
+      <c r="L37" s="0">
+        <v>0.99969338263622698</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0.00030661736377302073</v>
+      </c>
+      <c r="N37" s="0">
+        <v>0.89863530940744452</v>
+      </c>
+      <c r="O37" s="0">
+        <v>-75.739175368098273</v>
+      </c>
+      <c r="P37" s="0">
+        <v>113.63698925799801</v>
+      </c>
+      <c r="Q37" s="0">
+        <v>37.89781388989973</v>
+      </c>
+      <c r="R37" s="0">
+        <v>133.59563653841681</v>
+      </c>
+      <c r="S37" s="0">
+        <v>336.6033201553164</v>
+      </c>
+      <c r="T37" s="0">
+        <v>401.69698963922474</v>
+      </c>
+      <c r="U37" s="0">
+        <v>443.68423908653949</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0">
+        <v>4</v>
+      </c>
+      <c r="B38" s="0">
+        <v>0</v>
+      </c>
+      <c r="C38" s="0">
+        <v>0</v>
+      </c>
+      <c r="D38" s="0">
+        <v>52.930900209997752</v>
+      </c>
+      <c r="E38" s="0">
+        <v>573.29913437847358</v>
+      </c>
+      <c r="F38" s="0">
+        <v>232.5095571445645</v>
+      </c>
+      <c r="G38" s="0">
+        <v>62.961668678360773</v>
+      </c>
+      <c r="H38" s="0">
+        <v>29.373320685857379</v>
+      </c>
+      <c r="I38" s="0">
+        <v>7.6650106357818508</v>
+      </c>
+      <c r="J38" s="0">
+        <v>438.10823910009196</v>
+      </c>
+      <c r="K38" s="0">
+        <v>438.10825634392972</v>
+      </c>
+      <c r="L38" s="0">
+        <v>0.44025804501636667</v>
+      </c>
+      <c r="M38" s="0">
+        <v>0.55974195498363333</v>
+      </c>
+      <c r="N38" s="0">
+        <v>0.9082232634766334</v>
+      </c>
+      <c r="O38" s="0">
+        <v>-75.72664455113474</v>
+      </c>
+      <c r="P38" s="0">
+        <v>114.59136515451297</v>
+      </c>
+      <c r="Q38" s="0">
+        <v>38.864720603378224</v>
+      </c>
+      <c r="R38" s="0">
+        <v>129.9198882103928</v>
+      </c>
+      <c r="S38" s="0">
+        <v>465.76691524278385</v>
+      </c>
+      <c r="T38" s="0">
+        <v>659.66467305057131</v>
+      </c>
+      <c r="U38" s="0">
+        <v>787.52151254635464</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0">
+        <v>4</v>
+      </c>
+      <c r="B39" s="0">
+        <v>0</v>
+      </c>
+      <c r="C39" s="0">
+        <v>0</v>
+      </c>
+      <c r="D39" s="0">
+        <v>52.896663960672143</v>
+      </c>
+      <c r="E39" s="0">
+        <v>567.35918931664924</v>
+      </c>
+      <c r="F39" s="0">
+        <v>230.29658185855169</v>
+      </c>
+      <c r="G39" s="0">
+        <v>62.982964710715216</v>
+      </c>
+      <c r="H39" s="0">
+        <v>29.354886726887656</v>
+      </c>
+      <c r="I39" s="0">
+        <v>7.6621485623971211</v>
+      </c>
+      <c r="J39" s="0">
+        <v>439.86576413524534</v>
+      </c>
+      <c r="K39" s="0">
+        <v>439.98390560270315</v>
+      </c>
+      <c r="L39" s="0">
+        <v>0.56635802478735087</v>
+      </c>
+      <c r="M39" s="0">
+        <v>0.43364197521264913</v>
+      </c>
+      <c r="N39" s="0">
+        <v>0.90924025746459236</v>
+      </c>
+      <c r="O39" s="0">
+        <v>-75.72664455113474</v>
+      </c>
+      <c r="P39" s="0">
+        <v>114.7700926231777</v>
+      </c>
+      <c r="Q39" s="0">
+        <v>39.043448072042963</v>
+      </c>
+      <c r="R39" s="0">
+        <v>132.66493983060667</v>
+      </c>
+      <c r="S39" s="0">
+        <v>466.37513860366016</v>
+      </c>
+      <c r="T39" s="0">
+        <v>661.96889944872783</v>
+      </c>
+      <c r="U39" s="0">
+        <v>791.29851905423493</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0">
+        <v>4</v>
+      </c>
+      <c r="B40" s="0">
+        <v>0</v>
+      </c>
+      <c r="C40" s="0">
+        <v>0</v>
+      </c>
+      <c r="D40" s="0">
+        <v>52.896663960672143</v>
+      </c>
+      <c r="E40" s="0">
+        <v>572.31443285077341</v>
+      </c>
+      <c r="F40" s="0">
+        <v>230.86073154683709</v>
+      </c>
+      <c r="G40" s="0">
+        <v>62.915509971344939</v>
+      </c>
+      <c r="H40" s="0">
+        <v>29.419520197043713</v>
+      </c>
+      <c r="I40" s="0">
+        <v>7.6649698316113515</v>
+      </c>
+      <c r="J40" s="0">
+        <v>438.14313001817601</v>
+      </c>
+      <c r="K40" s="0">
+        <v>438.15110557332002</v>
+      </c>
+      <c r="L40" s="0">
+        <v>0.56006178202377688</v>
+      </c>
+      <c r="M40" s="0">
+        <v>0.43993821797622312</v>
+      </c>
+      <c r="N40" s="0">
+        <v>0.90866754934787075</v>
+      </c>
+      <c r="O40" s="0">
+        <v>-75.72664455113474</v>
+      </c>
+      <c r="P40" s="0">
+        <v>114.59136515451297</v>
+      </c>
+      <c r="Q40" s="0">
+        <v>38.864720603378224</v>
+      </c>
+      <c r="R40" s="0">
+        <v>129.9198882103928</v>
+      </c>
+      <c r="S40" s="0">
+        <v>465.76691524278385</v>
+      </c>
+      <c r="T40" s="0">
+        <v>659.66467305057131</v>
+      </c>
+      <c r="U40" s="0">
+        <v>787.52151254635464</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0">
+        <v>4</v>
+      </c>
+      <c r="B41" s="0">
+        <v>0</v>
+      </c>
+      <c r="C41" s="0">
+        <v>0</v>
+      </c>
+      <c r="D41" s="0">
+        <v>52.896663960672143</v>
+      </c>
+      <c r="E41" s="0">
+        <v>567.35918931664924</v>
+      </c>
+      <c r="F41" s="0">
+        <v>230.29658185855169</v>
+      </c>
+      <c r="G41" s="0">
+        <v>62.982964710715216</v>
+      </c>
+      <c r="H41" s="0">
+        <v>29.354886726887656</v>
+      </c>
+      <c r="I41" s="0">
+        <v>7.6621485623971211</v>
+      </c>
+      <c r="J41" s="0">
+        <v>439.86576413524534</v>
+      </c>
+      <c r="K41" s="0">
+        <v>439.98390560270315</v>
+      </c>
+      <c r="L41" s="0">
+        <v>0.56635802478735087</v>
+      </c>
+      <c r="M41" s="0">
+        <v>0.43364197521264913</v>
+      </c>
+      <c r="N41" s="0">
+        <v>0.90924025746459236</v>
+      </c>
+      <c r="O41" s="0">
+        <v>-75.72664455113474</v>
+      </c>
+      <c r="P41" s="0">
+        <v>114.7700926231777</v>
+      </c>
+      <c r="Q41" s="0">
+        <v>39.043448072042963</v>
+      </c>
+      <c r="R41" s="0">
+        <v>132.66493983060667</v>
+      </c>
+      <c r="S41" s="0">
+        <v>466.37513860366016</v>
+      </c>
+      <c r="T41" s="0">
+        <v>661.96889944872783</v>
+      </c>
+      <c r="U41" s="0">
+        <v>791.29851905423493</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0">
+        <v>4</v>
+      </c>
+      <c r="B42" s="0">
+        <v>0</v>
+      </c>
+      <c r="C42" s="0">
+        <v>0</v>
+      </c>
+      <c r="D42" s="0">
+        <v>52.948858691350836</v>
+      </c>
+      <c r="E42" s="0">
+        <v>564.84183825056834</v>
+      </c>
+      <c r="F42" s="0">
+        <v>229.2266296547441</v>
+      </c>
+      <c r="G42" s="0">
+        <v>62.963391275015624</v>
+      </c>
+      <c r="H42" s="0">
+        <v>29.383600319904779</v>
+      </c>
+      <c r="I42" s="0">
+        <v>7.6530084050795883</v>
+      </c>
+      <c r="J42" s="0">
+        <v>441.35536813234182</v>
+      </c>
+      <c r="K42" s="0">
+        <v>441.35538316296777</v>
+      </c>
+      <c r="L42" s="0">
+        <v>0.56125649712679571</v>
+      </c>
+      <c r="M42" s="0">
+        <v>0.43874350287320429</v>
+      </c>
+      <c r="N42" s="0">
+        <v>0.90911690294145975</v>
+      </c>
+      <c r="O42" s="0">
+        <v>-75.72664455113474</v>
+      </c>
+      <c r="P42" s="0">
+        <v>114.7700926231777</v>
+      </c>
+      <c r="Q42" s="0">
+        <v>39.043448072042963</v>
+      </c>
+      <c r="R42" s="0">
+        <v>132.66493983060667</v>
+      </c>
+      <c r="S42" s="0">
+        <v>466.37513860366016</v>
+      </c>
+      <c r="T42" s="0">
+        <v>661.96889944872783</v>
+      </c>
+      <c r="U42" s="0">
+        <v>791.29851905423493</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0">
+        <v>4</v>
+      </c>
+      <c r="B43" s="0">
+        <v>0</v>
+      </c>
+      <c r="C43" s="0">
+        <v>0</v>
+      </c>
+      <c r="D43" s="0">
+        <v>52.948858691350836</v>
+      </c>
+      <c r="E43" s="0">
+        <v>564.84183825056834</v>
+      </c>
+      <c r="F43" s="0">
+        <v>229.2266296547441</v>
+      </c>
+      <c r="G43" s="0">
+        <v>62.963391275015624</v>
+      </c>
+      <c r="H43" s="0">
+        <v>29.383600319904779</v>
+      </c>
+      <c r="I43" s="0">
+        <v>7.6530084050795883</v>
+      </c>
+      <c r="J43" s="0">
+        <v>441.35536813234182</v>
+      </c>
+      <c r="K43" s="0">
+        <v>441.35538316296777</v>
+      </c>
+      <c r="L43" s="0">
+        <v>0.56125649712679571</v>
+      </c>
+      <c r="M43" s="0">
+        <v>0.43874350287320429</v>
+      </c>
+      <c r="N43" s="0">
+        <v>0.90911690294145975</v>
+      </c>
+      <c r="O43" s="0">
+        <v>-75.72664455113474</v>
+      </c>
+      <c r="P43" s="0">
+        <v>114.7700926231777</v>
+      </c>
+      <c r="Q43" s="0">
+        <v>39.043448072042963</v>
+      </c>
+      <c r="R43" s="0">
+        <v>132.66493983060667</v>
+      </c>
+      <c r="S43" s="0">
+        <v>466.37513860366016</v>
+      </c>
+      <c r="T43" s="0">
+        <v>661.96889944872783</v>
+      </c>
+      <c r="U43" s="0">
+        <v>791.29851905423493</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0">
+        <v>4</v>
+      </c>
+      <c r="B44" s="0">
+        <v>2</v>
+      </c>
+      <c r="C44" s="0">
+        <v>30</v>
+      </c>
+      <c r="D44" s="0">
+        <v>46.448331109942089</v>
+      </c>
+      <c r="E44" s="0">
+        <v>335.60624515764238</v>
+      </c>
+      <c r="F44" s="0">
+        <v>148.78183463078676</v>
+      </c>
+      <c r="G44" s="0">
+        <v>57.797097093091075</v>
+      </c>
+      <c r="H44" s="0">
+        <v>33.981012007986998</v>
+      </c>
+      <c r="I44" s="0">
+        <v>8.221890898921929</v>
+      </c>
+      <c r="J44" s="0">
+        <v>392.74446804456198</v>
+      </c>
+      <c r="K44" s="0">
+        <v>392.74456212790801</v>
+      </c>
+      <c r="L44" s="0">
+        <v>0.23448834384974693</v>
+      </c>
+      <c r="M44" s="0">
+        <v>0.76551165615025307</v>
+      </c>
+      <c r="N44" s="0">
+        <v>0.93018443915544347</v>
+      </c>
+      <c r="O44" s="0">
+        <v>-75.727917205918246</v>
+      </c>
+      <c r="P44" s="0">
+        <v>110.00176691984746</v>
+      </c>
+      <c r="Q44" s="0">
+        <v>34.273849713929216</v>
+      </c>
+      <c r="R44" s="0">
+        <v>137.3979540130097</v>
+      </c>
+      <c r="S44" s="0">
+        <v>359.51800461089988</v>
+      </c>
+      <c r="T44" s="0">
+        <v>470.25884595470598</v>
+      </c>
+      <c r="U44" s="0">
+        <v>556.40819326298697</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0">
+        <v>3</v>
+      </c>
+      <c r="B45" s="0">
+        <v>2</v>
+      </c>
+      <c r="C45" s="0">
+        <v>30</v>
+      </c>
+      <c r="D45" s="0">
+        <v>46.329755063582127</v>
+      </c>
+      <c r="E45" s="0">
+        <v>340.77170738310537</v>
+      </c>
+      <c r="F45" s="0">
+        <v>143.81911833471895</v>
+      </c>
+      <c r="G45" s="0">
+        <v>63.440002180714508</v>
+      </c>
+      <c r="H45" s="0">
+        <v>28.725412479726153</v>
+      </c>
+      <c r="I45" s="0">
+        <v>7.8345853395593306</v>
+      </c>
+      <c r="J45" s="0">
+        <v>385.58750330104681</v>
+      </c>
+      <c r="K45" s="0">
+        <v>385.58751688197532</v>
+      </c>
+      <c r="L45" s="0">
+        <v>0.21861106311443756</v>
+      </c>
+      <c r="M45" s="0">
+        <v>0.78138893688556244</v>
+      </c>
+      <c r="N45" s="0">
+        <v>0.91424866505461755</v>
+      </c>
+      <c r="O45" s="0">
+        <v>-75.727921821937727</v>
+      </c>
+      <c r="P45" s="0">
+        <v>109.02933084128748</v>
+      </c>
+      <c r="Q45" s="0">
+        <v>33.301409019349748</v>
+      </c>
+      <c r="R45" s="0">
+        <v>129.05892706859547</v>
+      </c>
+      <c r="S45" s="0">
+        <v>354.61987168411179</v>
+      </c>
+      <c r="T45" s="0">
+        <v>457.82082930860088</v>
+      </c>
+      <c r="U45" s="0">
+        <v>528.90429182358457</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0">
+        <v>2</v>
+      </c>
+      <c r="B46" s="0">
+        <v>2</v>
+      </c>
+      <c r="C46" s="0">
+        <v>30</v>
+      </c>
+      <c r="D46" s="0">
+        <v>46.968665064360401</v>
+      </c>
+      <c r="E46" s="0">
+        <v>340.94304114393321</v>
+      </c>
+      <c r="F46" s="0">
+        <v>150.12436692049232</v>
+      </c>
+      <c r="G46" s="0">
+        <v>56.700693097201224</v>
+      </c>
+      <c r="H46" s="0">
+        <v>35.104144156936272</v>
+      </c>
+      <c r="I46" s="0">
+        <v>8.1951627458625111</v>
+      </c>
+      <c r="J46" s="0">
+        <v>356.95380315102273</v>
+      </c>
+      <c r="K46" s="0">
+        <v>356.98185922705147</v>
+      </c>
+      <c r="L46" s="0">
+        <v>0.8983680234993443</v>
+      </c>
+      <c r="M46" s="0">
+        <v>0.1016319765006557</v>
+      </c>
+      <c r="N46" s="0">
+        <v>0.93461130644925616</v>
+      </c>
+      <c r="O46" s="0">
+        <v>-75.727917205887806</v>
+      </c>
+      <c r="P46" s="0">
+        <v>109.59503804874097</v>
+      </c>
+      <c r="Q46" s="0">
+        <v>33.867120842853176</v>
+      </c>
+      <c r="R46" s="0">
+        <v>136.95399185200753</v>
+      </c>
+      <c r="S46" s="0">
+        <v>334.32702031402096</v>
+      </c>
+      <c r="T46" s="0">
+        <v>424.05827583844075</v>
+      </c>
+      <c r="U46" s="0">
+        <v>503.73704462554906</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/For Drug Challenge/Simulation_Results_Log.xlsx
+++ b/For Drug Challenge/Simulation_Results_Log.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="11_324AE617CF19DF2F225B9B65E4012D160102563D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61076E25-4958-4AFB-8AD8-B99E479DC21A}"/>
   <bookViews>
-    <workbookView xWindow="-31065" yWindow="9660" windowWidth="28020" windowHeight="14040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31065" yWindow="9660" windowWidth="28020" windowHeight="14040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="21" uniqueCount="21">
   <si>
     <t>Model</t>
   </si>
@@ -101,8 +101,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -116,7 +116,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -124,12 +124,14 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -152,7 +154,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -303,7 +305,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -327,9 +329,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -353,7 +355,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -388,7 +390,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -406,7 +408,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -431,7 +433,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -467,25 +469,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U30"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.21875" customWidth="1"/>
-    <col min="2" max="2" width="4.77734375" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" customWidth="1"/>
-    <col min="5" max="10" width="11.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.77734375" customWidth="1"/>
-    <col min="12" max="13" width="15.5546875" customWidth="1"/>
-    <col min="14" max="14" width="18.5546875" customWidth="1"/>
-    <col min="15" max="15" width="12.21875" customWidth="1"/>
-    <col min="16" max="17" width="11.5546875" customWidth="1"/>
-    <col min="18" max="18" width="13.109375" customWidth="1"/>
-    <col min="19" max="21" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.21875" customWidth="true"/>
+    <col min="2" max="2" width="4.77734375" customWidth="true"/>
+    <col min="3" max="3" width="5.109375" customWidth="true"/>
+    <col min="4" max="4" width="14.33203125" customWidth="true"/>
+    <col min="5" max="5" width="11.5546875" customWidth="true"/>
+    <col min="11" max="11" width="11.77734375" customWidth="true"/>
+    <col min="12" max="12" width="15.5546875" customWidth="true"/>
+    <col min="14" max="14" width="18.5546875" customWidth="true"/>
+    <col min="15" max="15" width="12.21875" customWidth="true"/>
+    <col min="16" max="16" width="11.5546875" customWidth="true"/>
+    <col min="18" max="18" width="13.109375" customWidth="true"/>
+    <col min="19" max="19" width="11.5546875" customWidth="true"/>
+    <col min="6" max="6" width="11.5546875" customWidth="true"/>
+    <col min="7" max="7" width="11.5546875" customWidth="true"/>
+    <col min="8" max="8" width="11.5546875" customWidth="true"/>
+    <col min="9" max="9" width="11.5546875" customWidth="true"/>
+    <col min="10" max="10" width="11.5546875" customWidth="true"/>
+    <col min="13" max="13" width="15.5546875" customWidth="true"/>
+    <col min="17" max="17" width="11.5546875" customWidth="true"/>
+    <col min="20" max="20" width="11.5546875" customWidth="true"/>
+    <col min="21" max="21" width="11.5546875" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -550,7 +561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -615,7 +626,7 @@
         <v>445.15774089237721</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -680,7 +691,7 @@
         <v>612.53106459655555</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -745,7 +756,7 @@
         <v>624.32699643900833</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -810,7 +821,7 @@
         <v>749.59288546012294</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -875,7 +886,7 @@
         <v>774.87230480672224</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0</v>
       </c>
@@ -940,7 +951,7 @@
         <v>443.10608322380904</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1005,7 +1016,7 @@
         <v>612.01806178589959</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1070,7 +1081,7 @@
         <v>621.48202972051695</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1135,7 +1146,7 @@
         <v>752.87191218775297</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1200,7 +1211,7 @@
         <v>765.27259589526784</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0</v>
       </c>
@@ -1265,7 +1276,7 @@
         <v>444.7117315806081</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -1330,7 +1341,7 @@
         <v>610.14847538790673</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1395,7 +1406,7 @@
         <v>620.08098036044885</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>3</v>
       </c>
@@ -1460,7 +1471,7 @@
         <v>743.75082824049787</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>4</v>
       </c>
@@ -1525,7 +1536,7 @@
         <v>763.740094575076</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0</v>
       </c>
@@ -1590,7 +1601,7 @@
         <v>444.8873856820519</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -1655,7 +1666,7 @@
         <v>608.07351869433296</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1720,7 +1731,7 @@
         <v>615.63409556269471</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1785,7 +1796,7 @@
         <v>739.16884492881218</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>4</v>
       </c>
@@ -1848,6 +1859,591 @@
       </c>
       <c r="U21">
         <v>748.97339891578849</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>4</v>
+      </c>
+      <c r="B22" s="0">
+        <v>2</v>
+      </c>
+      <c r="C22" s="0">
+        <v>100</v>
+      </c>
+      <c r="D22" s="0">
+        <v>42.913920157355903</v>
+      </c>
+      <c r="E22" s="0">
+        <v>244.14641275510769</v>
+      </c>
+      <c r="F22" s="0">
+        <v>156.84456525247788</v>
+      </c>
+      <c r="G22" s="0">
+        <v>55.503071008308602</v>
+      </c>
+      <c r="H22" s="0">
+        <v>35.918269146867452</v>
+      </c>
+      <c r="I22" s="0">
+        <v>8.5786598448239371</v>
+      </c>
+      <c r="J22" s="0">
+        <v>373.84958953975536</v>
+      </c>
+      <c r="K22" s="0">
+        <v>373.84966395888449</v>
+      </c>
+      <c r="L22" s="0">
+        <v>0.99186541242400694</v>
+      </c>
+      <c r="M22" s="0">
+        <v>0.0081345875759930575</v>
+      </c>
+      <c r="N22" s="0">
+        <v>0.93296967263549335</v>
+      </c>
+      <c r="O22" s="0">
+        <v>-75.728306505951252</v>
+      </c>
+      <c r="P22" s="0">
+        <v>102.22480007243072</v>
+      </c>
+      <c r="Q22" s="0">
+        <v>26.496493566479469</v>
+      </c>
+      <c r="R22" s="0">
+        <v>121.30415278154594</v>
+      </c>
+      <c r="S22" s="0">
+        <v>344.04932095109325</v>
+      </c>
+      <c r="T22" s="0">
+        <v>426.71008868054741</v>
+      </c>
+      <c r="U22" s="0">
+        <v>496.19891012479638</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>4</v>
+      </c>
+      <c r="B23" s="0">
+        <v>2</v>
+      </c>
+      <c r="C23" s="0">
+        <v>200</v>
+      </c>
+      <c r="D23" s="0">
+        <v>40.42567114810447</v>
+      </c>
+      <c r="E23" s="0">
+        <v>189.35747153390992</v>
+      </c>
+      <c r="F23" s="0">
+        <v>161.36254074325825</v>
+      </c>
+      <c r="G23" s="0">
+        <v>51.860928961709973</v>
+      </c>
+      <c r="H23" s="0">
+        <v>39.135910252303098</v>
+      </c>
+      <c r="I23" s="0">
+        <v>9.0031607859869265</v>
+      </c>
+      <c r="J23" s="0">
+        <v>332.29777755356793</v>
+      </c>
+      <c r="K23" s="0">
+        <v>333.47099073068682</v>
+      </c>
+      <c r="L23" s="0">
+        <v>0.97268180479397892</v>
+      </c>
+      <c r="M23" s="0">
+        <v>0.027318195206021079</v>
+      </c>
+      <c r="N23" s="0">
+        <v>0.94184967215915594</v>
+      </c>
+      <c r="O23" s="0">
+        <v>-75.72842307261476</v>
+      </c>
+      <c r="P23" s="0">
+        <v>96.633452863376959</v>
+      </c>
+      <c r="Q23" s="0">
+        <v>20.905029790762196</v>
+      </c>
+      <c r="R23" s="0">
+        <v>124.052495517411</v>
+      </c>
+      <c r="S23" s="0">
+        <v>299.50625310685882</v>
+      </c>
+      <c r="T23" s="0">
+        <v>366.06246921662841</v>
+      </c>
+      <c r="U23" s="0">
+        <v>427.14435696349483</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0">
+        <v>4</v>
+      </c>
+      <c r="B24" s="0">
+        <v>1</v>
+      </c>
+      <c r="C24" s="0">
+        <v>15</v>
+      </c>
+      <c r="D24" s="0">
+        <v>51.825064679478217</v>
+      </c>
+      <c r="E24" s="0">
+        <v>576.27516495942029</v>
+      </c>
+      <c r="F24" s="0">
+        <v>205.81742929112625</v>
+      </c>
+      <c r="G24" s="0">
+        <v>56.998883955324231</v>
+      </c>
+      <c r="H24" s="0">
+        <v>34.971395564619314</v>
+      </c>
+      <c r="I24" s="0">
+        <v>8.0297204800564597</v>
+      </c>
+      <c r="J24" s="0">
+        <v>423.32078747809578</v>
+      </c>
+      <c r="K24" s="0">
+        <v>423.33029621400868</v>
+      </c>
+      <c r="L24" s="0">
+        <v>0.88414253263824893</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.11585746736175108</v>
+      </c>
+      <c r="N24" s="0">
+        <v>0.91203886564785608</v>
+      </c>
+      <c r="O24" s="0">
+        <v>-75.726879399764101</v>
+      </c>
+      <c r="P24" s="0">
+        <v>114.95713592325546</v>
+      </c>
+      <c r="Q24" s="0">
+        <v>39.23025652349137</v>
+      </c>
+      <c r="R24" s="0">
+        <v>74.901448200781559</v>
+      </c>
+      <c r="S24" s="0">
+        <v>461.71072469425599</v>
+      </c>
+      <c r="T24" s="0">
+        <v>642.1488290984089</v>
+      </c>
+      <c r="U24" s="0">
+        <v>740.26972640437634</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0">
+        <v>4</v>
+      </c>
+      <c r="B25" s="0">
+        <v>1</v>
+      </c>
+      <c r="C25" s="0">
+        <v>15</v>
+      </c>
+      <c r="D25" s="0">
+        <v>51.825064679478217</v>
+      </c>
+      <c r="E25" s="0">
+        <v>576.27516495942029</v>
+      </c>
+      <c r="F25" s="0">
+        <v>205.81742929112625</v>
+      </c>
+      <c r="G25" s="0">
+        <v>56.998883955324231</v>
+      </c>
+      <c r="H25" s="0">
+        <v>34.971395564619314</v>
+      </c>
+      <c r="I25" s="0">
+        <v>8.0297204800564597</v>
+      </c>
+      <c r="J25" s="0">
+        <v>423.32078747809578</v>
+      </c>
+      <c r="K25" s="0">
+        <v>423.33029621400868</v>
+      </c>
+      <c r="L25" s="0">
+        <v>0.88414253263824893</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.11585746736175108</v>
+      </c>
+      <c r="N25" s="0">
+        <v>0.91203886564785608</v>
+      </c>
+      <c r="O25" s="0">
+        <v>-75.726879399764101</v>
+      </c>
+      <c r="P25" s="0">
+        <v>114.95713592325546</v>
+      </c>
+      <c r="Q25" s="0">
+        <v>39.23025652349137</v>
+      </c>
+      <c r="R25" s="0">
+        <v>74.901448200781559</v>
+      </c>
+      <c r="S25" s="0">
+        <v>461.71072469425599</v>
+      </c>
+      <c r="T25" s="0">
+        <v>642.1488290984089</v>
+      </c>
+      <c r="U25" s="0">
+        <v>740.26972640437634</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0">
+        <v>4</v>
+      </c>
+      <c r="B26" s="0">
+        <v>2</v>
+      </c>
+      <c r="C26" s="0">
+        <v>200</v>
+      </c>
+      <c r="D26" s="0">
+        <v>40.274014252055466</v>
+      </c>
+      <c r="E26" s="0">
+        <v>187.80654055743616</v>
+      </c>
+      <c r="F26" s="0">
+        <v>160.22280478768698</v>
+      </c>
+      <c r="G26" s="0">
+        <v>51.732066573263879</v>
+      </c>
+      <c r="H26" s="0">
+        <v>39.258781543621069</v>
+      </c>
+      <c r="I26" s="0">
+        <v>9.009151883115047</v>
+      </c>
+      <c r="J26" s="0">
+        <v>334.62137079610983</v>
+      </c>
+      <c r="K26" s="0">
+        <v>335.83004539008448</v>
+      </c>
+      <c r="L26" s="0">
+        <v>0.97227100017591717</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.027728999824082834</v>
+      </c>
+      <c r="N26" s="0">
+        <v>0.94178044055143995</v>
+      </c>
+      <c r="O26" s="0">
+        <v>-75.72842307261476</v>
+      </c>
+      <c r="P26" s="0">
+        <v>96.633452863376959</v>
+      </c>
+      <c r="Q26" s="0">
+        <v>20.905029790762196</v>
+      </c>
+      <c r="R26" s="0">
+        <v>124.052495517411</v>
+      </c>
+      <c r="S26" s="0">
+        <v>299.50625310685882</v>
+      </c>
+      <c r="T26" s="0">
+        <v>366.06246921662841</v>
+      </c>
+      <c r="U26" s="0">
+        <v>427.14435696349483</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>4</v>
+      </c>
+      <c r="B27" s="0">
+        <v>2</v>
+      </c>
+      <c r="C27" s="0">
+        <v>300</v>
+      </c>
+      <c r="D27" s="0">
+        <v>38.631671909763959</v>
+      </c>
+      <c r="E27" s="0">
+        <v>159.41640260872009</v>
+      </c>
+      <c r="F27" s="0">
+        <v>163.30723752801896</v>
+      </c>
+      <c r="G27" s="0">
+        <v>48.765203276508714</v>
+      </c>
+      <c r="H27" s="0">
+        <v>41.907742000414295</v>
+      </c>
+      <c r="I27" s="0">
+        <v>9.3270547230769871</v>
+      </c>
+      <c r="J27" s="0">
+        <v>305.90929773248263</v>
+      </c>
+      <c r="K27" s="0">
+        <v>312.31961408600864</v>
+      </c>
+      <c r="L27" s="0">
+        <v>0.99962149322780525</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.00037850677219475326</v>
+      </c>
+      <c r="N27" s="0">
+        <v>0.95025792016389776</v>
+      </c>
+      <c r="O27" s="0">
+        <v>-75.728465647123997</v>
+      </c>
+      <c r="P27" s="0">
+        <v>95.487487591009938</v>
+      </c>
+      <c r="Q27" s="0">
+        <v>19.759021943885948</v>
+      </c>
+      <c r="R27" s="0">
+        <v>115.55841560203844</v>
+      </c>
+      <c r="S27" s="0">
+        <v>260.77261967734194</v>
+      </c>
+      <c r="T27" s="0">
+        <v>326.6976001095336</v>
+      </c>
+      <c r="U27" s="0">
+        <v>388.98012460368045</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>0</v>
+      </c>
+      <c r="B28" s="0">
+        <v>2</v>
+      </c>
+      <c r="C28" s="0">
+        <v>200</v>
+      </c>
+      <c r="D28" s="0">
+        <v>37.000638184882597</v>
+      </c>
+      <c r="E28" s="0">
+        <v>179.82731426700303</v>
+      </c>
+      <c r="F28" s="0">
+        <v>153.41997806300787</v>
+      </c>
+      <c r="G28" s="0">
+        <v>45.231204514215605</v>
+      </c>
+      <c r="H28" s="0">
+        <v>45.364591356696423</v>
+      </c>
+      <c r="I28" s="0">
+        <v>9.4042041290879848</v>
+      </c>
+      <c r="J28" s="0">
+        <v>251.38849041531856</v>
+      </c>
+      <c r="K28" s="0">
+        <v>251.44705246971833</v>
+      </c>
+      <c r="L28" s="0">
+        <v>0.90983344087702944</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.090166559122970558</v>
+      </c>
+      <c r="N28" s="0">
+        <v>0.95789965300735824</v>
+      </c>
+      <c r="O28" s="0">
+        <v>-75.740978230225579</v>
+      </c>
+      <c r="P28" s="0">
+        <v>89.733510525939892</v>
+      </c>
+      <c r="Q28" s="0">
+        <v>13.992532295714312</v>
+      </c>
+      <c r="R28" s="0">
+        <v>103.34164352297101</v>
+      </c>
+      <c r="S28" s="0">
+        <v>233.84412117084503</v>
+      </c>
+      <c r="T28" s="0">
+        <v>262.15829456207211</v>
+      </c>
+      <c r="U28" s="0">
+        <v>288.89203945888221</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>4</v>
+      </c>
+      <c r="B29" s="0">
+        <v>2</v>
+      </c>
+      <c r="C29" s="0">
+        <v>200</v>
+      </c>
+      <c r="D29" s="0">
+        <v>38.462416408453919</v>
+      </c>
+      <c r="E29" s="0">
+        <v>178.15455181366258</v>
+      </c>
+      <c r="F29" s="0">
+        <v>154.33744399454736</v>
+      </c>
+      <c r="G29" s="0">
+        <v>48.046211841692674</v>
+      </c>
+      <c r="H29" s="0">
+        <v>42.629208672731359</v>
+      </c>
+      <c r="I29" s="0">
+        <v>9.3245794855759634</v>
+      </c>
+      <c r="J29" s="0">
+        <v>343.86945106473837</v>
+      </c>
+      <c r="K29" s="0">
+        <v>344.05646235301128</v>
+      </c>
+      <c r="L29" s="0">
+        <v>0.99139638908966299</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0.0086036109103370118</v>
+      </c>
+      <c r="N29" s="0">
+        <v>0.94533621830287307</v>
+      </c>
+      <c r="O29" s="0">
+        <v>-75.72842307261476</v>
+      </c>
+      <c r="P29" s="0">
+        <v>96.633452863376959</v>
+      </c>
+      <c r="Q29" s="0">
+        <v>20.905029790762196</v>
+      </c>
+      <c r="R29" s="0">
+        <v>124.052495517411</v>
+      </c>
+      <c r="S29" s="0">
+        <v>299.50625310685882</v>
+      </c>
+      <c r="T29" s="0">
+        <v>366.06246921662841</v>
+      </c>
+      <c r="U29" s="0">
+        <v>427.14435696349483</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>0</v>
+      </c>
+      <c r="B30" s="0">
+        <v>2</v>
+      </c>
+      <c r="C30" s="0">
+        <v>200</v>
+      </c>
+      <c r="D30" s="0">
+        <v>37.000638184882597</v>
+      </c>
+      <c r="E30" s="0">
+        <v>179.82731426700303</v>
+      </c>
+      <c r="F30" s="0">
+        <v>153.41997806300787</v>
+      </c>
+      <c r="G30" s="0">
+        <v>45.231204514215605</v>
+      </c>
+      <c r="H30" s="0">
+        <v>45.364591356696423</v>
+      </c>
+      <c r="I30" s="0">
+        <v>9.4042041290879848</v>
+      </c>
+      <c r="J30" s="0">
+        <v>251.38849041531856</v>
+      </c>
+      <c r="K30" s="0">
+        <v>251.44705246971833</v>
+      </c>
+      <c r="L30" s="0">
+        <v>0.90983344087702944</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.090166559122970558</v>
+      </c>
+      <c r="N30" s="0">
+        <v>0.95789965300735824</v>
+      </c>
+      <c r="O30" s="0">
+        <v>-75.740978230225579</v>
+      </c>
+      <c r="P30" s="0">
+        <v>89.733510525939892</v>
+      </c>
+      <c r="Q30" s="0">
+        <v>13.992532295714312</v>
+      </c>
+      <c r="R30" s="0">
+        <v>103.34164352297101</v>
+      </c>
+      <c r="S30" s="0">
+        <v>233.84412117084503</v>
+      </c>
+      <c r="T30" s="0">
+        <v>262.15829456207211</v>
+      </c>
+      <c r="U30" s="0">
+        <v>288.89203945888221</v>
       </c>
     </row>
   </sheetData>
